--- a/Sprint 10/dades_GrupC.xlsx
+++ b/Sprint 10/dades_GrupC.xlsx
@@ -3465,7 +3465,7 @@
         <v>36096</v>
       </c>
       <c r="P39" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>26241</v>
       </c>
       <c r="P113" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
